--- a/data/trans_dic/IP16A12_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre</t>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 38,49</t>
+          <t>12,6; 39,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 45,93</t>
+          <t>16,5; 47,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 38,67</t>
+          <t>18,52; 39,19</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 37,44</t>
+          <t>8,86; 36,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 43,57</t>
+          <t>12,65; 43,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 34,44</t>
+          <t>14,56; 35,48</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 59,1</t>
+          <t>11,3; 61,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 27,67</t>
+          <t>4,16; 25,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 32,14</t>
+          <t>9,64; 32,31</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 15,83</t>
+          <t>1,82; 16,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 27,58</t>
+          <t>10,37; 28,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 17,52</t>
+          <t>5,3; 18,06</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,4; 32,78</t>
+          <t>7,79; 31,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 31,55</t>
+          <t>9,32; 31,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 27,14</t>
+          <t>11,44; 27,0</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 36,26</t>
+          <t>3,16; 40,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 32,06</t>
+          <t>2,31; 32,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 26,26</t>
+          <t>4,19; 26,48</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 20,32</t>
+          <t>7,93; 20,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,16; 25,49</t>
+          <t>15,03; 25,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,04; 21,46</t>
+          <t>13,13; 21,18</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5791</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9507</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15299</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3131; 9727</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5265; 15311</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10511; 22244</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4785</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6049</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10834</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2077; 8520</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2971; 10206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6830; 16651</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2870</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4965</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1085; 5916</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>720; 4429</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2593; 8688</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5461</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9829</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15290</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1406; 12466</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5790; 15846</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7065; 24045</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11808</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2304; 9436</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3352; 11363</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7504; 17702</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3552</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>386; 4929</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>354; 4991</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1153; 7287</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>25669</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>36079</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>61748</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>14030; 35777</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>27021; 45764</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>46850; 75594</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A12_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 39,14</t>
+          <t>13,02; 37,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,5; 47,98</t>
+          <t>15,88; 46,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 39,19</t>
+          <t>17,67; 38,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 36,36</t>
+          <t>8,14; 35,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 43,45</t>
+          <t>12,67; 45,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 35,48</t>
+          <t>14,1; 34,6</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 61,65</t>
+          <t>10,94; 57,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 25,61</t>
+          <t>4,31; 28,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 32,31</t>
+          <t>9,71; 32,63</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 16,12</t>
+          <t>1,76; 14,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 28,37</t>
+          <t>10,23; 28,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 18,06</t>
+          <t>5,02; 17,97</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 31,89</t>
+          <t>8,13; 32,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 31,58</t>
+          <t>10,08; 31,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 27,0</t>
+          <t>11,55; 27,36</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,16; 40,34</t>
+          <t>3,32; 41,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 32,62</t>
+          <t>2,25; 31,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 26,48</t>
+          <t>4,82; 26,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 20,21</t>
+          <t>8,46; 20,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,03; 25,45</t>
+          <t>15,07; 26,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,13; 21,18</t>
+          <t>13,03; 21,3</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3131; 9727</t>
+          <t>3235; 9370</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5265; 15311</t>
+          <t>5067; 14896</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10511; 22244</t>
+          <t>10027; 22021</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2077; 8520</t>
+          <t>1907; 8301</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2971; 10206</t>
+          <t>2976; 10617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6830; 16651</t>
+          <t>6617; 16237</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1085; 5916</t>
+          <t>1050; 5478</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>720; 4429</t>
+          <t>746; 4891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2593; 8688</t>
+          <t>2611; 8775</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1406; 12466</t>
+          <t>1358; 11434</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5790; 15846</t>
+          <t>5715; 16098</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7065; 24045</t>
+          <t>6683; 23936</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2304; 9436</t>
+          <t>2406; 9503</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3352; 11363</t>
+          <t>3626; 11440</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7504; 17702</t>
+          <t>7576; 17940</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>386; 4929</t>
+          <t>405; 5090</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>354; 4991</t>
+          <t>344; 4797</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1153; 7287</t>
+          <t>1326; 7248</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14030; 35777</t>
+          <t>14971; 35520</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27021; 45764</t>
+          <t>27102; 46971</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46850; 75594</t>
+          <t>46501; 76007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Clase-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,02; 37,7</t>
+          <t>16,24; 46,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,88; 46,68</t>
+          <t>11,82; 38,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,67; 38,8</t>
+          <t>17,25; 38,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 35,43</t>
+          <t>12,2; 42,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 45,19</t>
+          <t>8,54; 38,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 34,6</t>
+          <t>13,96; 34,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 57,09</t>
+          <t>3,56; 30,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 28,28</t>
+          <t>11,05; 57,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 32,63</t>
+          <t>9,17; 32,95</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,79</t>
+          <t>10,04; 28,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 28,83</t>
+          <t>4,04; 15,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 17,97</t>
+          <t>8,71; 19,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 32,11</t>
+          <t>9,52; 32,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 31,8</t>
+          <t>7,96; 33,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 27,36</t>
+          <t>11,7; 27,86</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 41,65</t>
+          <t>1,79; 34,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 31,35</t>
+          <t>2,87; 41,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 26,34</t>
+          <t>5,32; 29,73</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 20,06</t>
+          <t>15,23; 25,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,07; 26,12</t>
+          <t>12,61; 22,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,03; 21,3</t>
+          <t>15,16; 22,68</t>
         </is>
       </c>
     </row>
@@ -927,18 +927,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>14395</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3235; 9370</t>
+          <t>4769; 13522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5067; 14896</t>
+          <t>2912; 9483</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10027; 22021</t>
+          <t>9317; 20734</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10458</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1907; 8301</t>
+          <t>2761; 9711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2976; 10617</t>
+          <t>1961; 8775</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6617; 16237</t>
+          <t>6368; 15719</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4602</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1050; 5478</t>
+          <t>535; 4530</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>746; 4891</t>
+          <t>1052; 5502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2611; 8775</t>
+          <t>2251; 8087</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>12576</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1358; 11434</t>
+          <t>4993; 14180</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5715; 16098</t>
+          <t>1756; 6756</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6683; 23936</t>
+          <t>8117; 18622</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11242</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2406; 9503</t>
+          <t>3063; 10539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3626; 11440</t>
+          <t>2340; 9709</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7576; 17940</t>
+          <t>7200; 17148</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3712</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>405; 5090</t>
+          <t>253; 4884</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>344; 4797</t>
+          <t>357; 5195</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1326; 7248</t>
+          <t>1415; 7898</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36079</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>56985</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14971; 35520</t>
+          <t>24826; 42365</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27102; 46971</t>
+          <t>17954; 31978</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46501; 76007</t>
+          <t>46293; 69281</t>
         </is>
       </c>
     </row>
